--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335165</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446027</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132445998</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446015</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446024</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,6 +1363,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446007</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1430,6 +1465,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446020</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446002</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1624,6 +1669,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446005</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1721,6 +1771,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446008</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1818,6 +1873,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446010</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1930,6 +1990,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446013</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2027,6 +2092,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446021</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2124,6 +2194,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132445997</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2221,6 +2296,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446001</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2318,6 +2398,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446003</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2415,6 +2500,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446018</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2512,6 +2602,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446031</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2609,6 +2704,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446004</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2706,6 +2806,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446012</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2803,6 +2908,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446017</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2900,6 +3010,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2997,6 +3112,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446011</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3109,6 +3229,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446019</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3222,6 +3347,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3335,6 +3465,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3448,6 +3583,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446028</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3565,6 +3705,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446023</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3682,6 +3827,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446079</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3800,6 +3950,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446074</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3917,6 +4072,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132445999</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4034,6 +4194,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446029</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4131,6 +4296,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446075</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4233,6 +4403,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335133</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4345,6 +4520,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121791393</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4442,6 +4622,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446006</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4539,6 +4724,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446030</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4636,6 +4826,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446073</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4748,6 +4943,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446009</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4860,8 +5060,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446014</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2100,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132445997</v>
+        <v>136097908</v>
       </c>
       <c r="B15" t="n">
-        <v>96501</v>
+        <v>96607</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,34 +2111,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>348634</v>
+        <v>348516</v>
       </c>
       <c r="R15" t="n">
-        <v>6519450</v>
+        <v>6519369</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,6 +2181,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2196,16 +2211,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132445997</t>
+          <t>https://artportalen.se/Sighting/136097908</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132446001</v>
+        <v>136097912</v>
       </c>
       <c r="B16" t="n">
-        <v>96501</v>
+        <v>96607</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,34 +2228,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>348660</v>
+        <v>348538</v>
       </c>
       <c r="R16" t="n">
-        <v>6519418</v>
+        <v>6519538</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2267,12 +2282,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,13 +2313,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446001</t>
+          <t>https://artportalen.se/Sighting/136097912</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132446003</v>
+        <v>132445997</v>
       </c>
       <c r="B17" t="n">
         <v>96501</v>
@@ -2339,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>348643</v>
+        <v>348634</v>
       </c>
       <c r="R17" t="n">
-        <v>6519393</v>
+        <v>6519450</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2400,13 +2415,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446003</t>
+          <t>https://artportalen.se/Sighting/132445997</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132446018</v>
+        <v>132446001</v>
       </c>
       <c r="B18" t="n">
         <v>96501</v>
@@ -2441,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>348663</v>
+        <v>348660</v>
       </c>
       <c r="R18" t="n">
-        <v>6519352</v>
+        <v>6519418</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2502,13 +2517,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446018</t>
+          <t>https://artportalen.se/Sighting/132446001</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132446031</v>
+        <v>132446003</v>
       </c>
       <c r="B19" t="n">
         <v>96501</v>
@@ -2539,14 +2554,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>348743</v>
+        <v>348643</v>
       </c>
       <c r="R19" t="n">
-        <v>6519161</v>
+        <v>6519393</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2604,16 +2619,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446031</t>
+          <t>https://artportalen.se/Sighting/132446003</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132446004</v>
+        <v>132446018</v>
       </c>
       <c r="B20" t="n">
-        <v>96306</v>
+        <v>96501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,21 +2636,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2660,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>348632</v>
+        <v>348663</v>
       </c>
       <c r="R20" t="n">
-        <v>6519384</v>
+        <v>6519352</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2706,16 +2721,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446004</t>
+          <t>https://artportalen.se/Sighting/132446018</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132446012</v>
+        <v>132446031</v>
       </c>
       <c r="B21" t="n">
-        <v>96306</v>
+        <v>96501</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,34 +2738,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>348647</v>
+        <v>348743</v>
       </c>
       <c r="R21" t="n">
-        <v>6519347</v>
+        <v>6519161</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2808,16 +2823,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446012</t>
+          <t>https://artportalen.se/Sighting/132446031</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132446017</v>
+        <v>136097911</v>
       </c>
       <c r="B22" t="n">
-        <v>96306</v>
+        <v>96356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,34 +2840,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2779</v>
+        <v>2676</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>348663</v>
+        <v>348538</v>
       </c>
       <c r="R22" t="n">
-        <v>6519352</v>
+        <v>6519538</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2879,12 +2894,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2910,13 +2925,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446017</t>
+          <t>https://artportalen.se/Sighting/136097911</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132446022</v>
+        <v>132446004</v>
       </c>
       <c r="B23" t="n">
         <v>96306</v>
@@ -2947,14 +2962,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>348678</v>
+        <v>348632</v>
       </c>
       <c r="R23" t="n">
-        <v>6519308</v>
+        <v>6519384</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3012,16 +3027,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446022</t>
+          <t>https://artportalen.se/Sighting/132446004</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132446011</v>
+        <v>132446012</v>
       </c>
       <c r="B24" t="n">
-        <v>96533</v>
+        <v>96306</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,21 +3044,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3053,10 +3068,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>348654</v>
+        <v>348647</v>
       </c>
       <c r="R24" t="n">
-        <v>6519348</v>
+        <v>6519347</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3114,16 +3129,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446011</t>
+          <t>https://artportalen.se/Sighting/132446012</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132446019</v>
+        <v>132446017</v>
       </c>
       <c r="B25" t="n">
-        <v>96533</v>
+        <v>96306</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,21 +3146,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3155,10 +3170,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>348662</v>
+        <v>348663</v>
       </c>
       <c r="R25" t="n">
-        <v>6519330</v>
+        <v>6519352</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3202,21 +3217,6 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446019</t>
+          <t>https://artportalen.se/Sighting/132446017</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132446025</v>
+        <v>132446022</v>
       </c>
       <c r="B26" t="n">
-        <v>92031</v>
+        <v>96306</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3248,21 +3248,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5321</v>
+        <v>2779</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>348701</v>
+        <v>348678</v>
       </c>
       <c r="R26" t="n">
-        <v>6519282</v>
+        <v>6519308</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3316,24 +3316,8 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3349,16 +3333,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446025</t>
+          <t>https://artportalen.se/Sighting/132446022</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132446026</v>
+        <v>136097914</v>
       </c>
       <c r="B27" t="n">
-        <v>92031</v>
+        <v>96401</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3366,34 +3350,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5321</v>
+        <v>2779</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>348708</v>
+        <v>348537</v>
       </c>
       <c r="R27" t="n">
-        <v>6519267</v>
+        <v>6519535</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3420,12 +3404,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3434,24 +3418,8 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3467,16 +3435,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446026</t>
+          <t>https://artportalen.se/Sighting/136097914</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132446028</v>
+        <v>132446011</v>
       </c>
       <c r="B28" t="n">
-        <v>92031</v>
+        <v>96533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3484,34 +3452,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5321</v>
+        <v>2818</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>348666</v>
+        <v>348654</v>
       </c>
       <c r="R28" t="n">
-        <v>6519254</v>
+        <v>6519348</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3552,24 +3520,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3585,16 +3537,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446028</t>
+          <t>https://artportalen.se/Sighting/132446011</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132446023</v>
+        <v>132446019</v>
       </c>
       <c r="B29" t="n">
-        <v>4776</v>
+        <v>96533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3602,39 +3554,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100299</v>
+        <v>2818</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>348665</v>
+        <v>348662</v>
       </c>
       <c r="R29" t="n">
-        <v>6519298</v>
+        <v>6519330</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3707,16 +3654,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446023</t>
+          <t>https://artportalen.se/Sighting/132446019</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132446079</v>
+        <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>4776</v>
+        <v>96628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,39 +3671,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100299</v>
+        <v>2818</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>348740</v>
+        <v>348719</v>
       </c>
       <c r="R30" t="n">
-        <v>6519761</v>
+        <v>6519093</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3783,12 +3725,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3829,16 +3771,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446079</t>
+          <t>https://artportalen.se/Sighting/136097899</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132446074</v>
+        <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>5181</v>
+        <v>96628</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3846,39 +3788,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>348747</v>
+        <v>348560</v>
       </c>
       <c r="R31" t="n">
-        <v>6519747</v>
+        <v>6519339</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3905,12 +3842,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3919,7 +3856,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3952,56 +3888,51 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446074</t>
+          <t>https://artportalen.se/Sighting/136097906</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132445999</v>
+        <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>8374</v>
+        <v>96628</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106540</v>
+        <v>2818</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>348665</v>
+        <v>348545</v>
       </c>
       <c r="R32" t="n">
-        <v>6519431</v>
+        <v>6519374</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4028,12 +3959,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4047,17 +3978,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4074,56 +4005,51 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132445999</t>
+          <t>https://artportalen.se/Sighting/136097907</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132446029</v>
+        <v>132446025</v>
       </c>
       <c r="B33" t="n">
-        <v>8374</v>
+        <v>92031</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106540</v>
+        <v>5321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>348623</v>
+        <v>348701</v>
       </c>
       <c r="R33" t="n">
-        <v>6519241</v>
+        <v>6519282</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4164,22 +4090,23 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4196,16 +4123,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446029</t>
+          <t>https://artportalen.se/Sighting/132446025</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132446075</v>
+        <v>132446026</v>
       </c>
       <c r="B34" t="n">
-        <v>8449</v>
+        <v>92031</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4213,34 +4140,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>5321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>348741</v>
+        <v>348708</v>
       </c>
       <c r="R34" t="n">
-        <v>6519743</v>
+        <v>6519267</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4281,8 +4208,24 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4298,54 +4241,54 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446075</t>
+          <t>https://artportalen.se/Sighting/132446026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132335133</v>
+        <v>132446028</v>
       </c>
       <c r="B35" t="n">
-        <v>101974</v>
+        <v>92031</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220075</v>
+        <v>5321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chrysosplenium alternifolium</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, ca 160 m NO om tjärnets norra ände, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>348563</v>
+        <v>348666</v>
       </c>
       <c r="R35" t="n">
-        <v>6519443</v>
+        <v>6519254</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4369,12 +4312,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4383,38 +4326,49 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Sumpskog med klibbal.</t>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335133</t>
+          <t>https://artportalen.se/Sighting/132446028</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121791393</v>
+        <v>132446023</v>
       </c>
       <c r="B36" t="n">
-        <v>101326</v>
+        <v>4776</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,47 +4376,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>348597</v>
+        <v>348665</v>
       </c>
       <c r="R36" t="n">
-        <v>6519354</v>
+        <v>6519298</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4486,12 +4435,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4503,35 +4452,45 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121791393</t>
+          <t>https://artportalen.se/Sighting/132446023</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132446006</v>
+        <v>132446079</v>
       </c>
       <c r="B37" t="n">
-        <v>101403</v>
+        <v>4776</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4539,34 +4498,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>348630</v>
+        <v>348740</v>
       </c>
       <c r="R37" t="n">
-        <v>6519376</v>
+        <v>6519761</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4610,6 +4574,21 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
@@ -4624,16 +4603,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446006</t>
+          <t>https://artportalen.se/Sighting/132446079</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132446030</v>
+        <v>132446074</v>
       </c>
       <c r="B38" t="n">
-        <v>101403</v>
+        <v>5181</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4641,34 +4620,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>348675</v>
+        <v>348747</v>
       </c>
       <c r="R38" t="n">
-        <v>6519199</v>
+        <v>6519747</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4709,8 +4693,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4726,16 +4726,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446030</t>
+          <t>https://artportalen.se/Sighting/132446074</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132446073</v>
+        <v>136097897</v>
       </c>
       <c r="B39" t="n">
-        <v>101403</v>
+        <v>5182</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4743,34 +4743,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skog söder om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>348729</v>
+        <v>348723</v>
       </c>
       <c r="R39" t="n">
-        <v>6519685</v>
+        <v>6519121</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4797,12 +4802,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4813,6 +4818,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4828,16 +4848,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446073</t>
+          <t>https://artportalen.se/Sighting/136097897</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132446009</v>
+        <v>136097898</v>
       </c>
       <c r="B40" t="n">
-        <v>80438</v>
+        <v>5202</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4845,34 +4865,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>105930</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>348626</v>
+        <v>348723</v>
       </c>
       <c r="R40" t="n">
-        <v>6519358</v>
+        <v>6519121</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4899,12 +4924,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4918,17 +4943,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4945,16 +4970,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446009</t>
+          <t>https://artportalen.se/Sighting/136097898</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132446014</v>
+        <v>136097942</v>
       </c>
       <c r="B41" t="n">
-        <v>80403</v>
+        <v>5202</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4962,34 +4987,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6003719</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>348655</v>
+        <v>348780</v>
       </c>
       <c r="R41" t="n">
-        <v>6519352</v>
+        <v>6519577</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5016,12 +5046,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5035,17 +5065,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5061,6 +5091,4181 @@
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097942</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132445999</v>
+      </c>
+      <c r="B42" t="n">
+        <v>8374</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Janses kulle, Dls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>348665</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6519431</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132445999</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132446029</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8374</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>348623</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6519241</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446029</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132446075</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>348741</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6519743</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446075</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136097896</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>348699</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6519187</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097896</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136097889</v>
+      </c>
+      <c r="B46" t="n">
+        <v>111586</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>348824</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6519586</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097889</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136097891</v>
+      </c>
+      <c r="B47" t="n">
+        <v>111586</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>348614</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6519482</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097891</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136097893</v>
+      </c>
+      <c r="B48" t="n">
+        <v>111586</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>348612</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6519392</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097893</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136097900</v>
+      </c>
+      <c r="B49" t="n">
+        <v>111586</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>348618</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6519260</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097900</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136097921</v>
+      </c>
+      <c r="B50" t="n">
+        <v>111586</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>348587</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6519511</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097921</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136097933</v>
+      </c>
+      <c r="B51" t="n">
+        <v>111586</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>348673</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6519697</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097933</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136097936</v>
+      </c>
+      <c r="B52" t="n">
+        <v>111586</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>348711</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6519665</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097936</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136097939</v>
+      </c>
+      <c r="B53" t="n">
+        <v>111586</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>348745</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6519603</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097939</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136097943</v>
+      </c>
+      <c r="B54" t="n">
+        <v>111586</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>348818</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6519588</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097943</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136097946</v>
+      </c>
+      <c r="B55" t="n">
+        <v>111586</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>348846</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6519619</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097946</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132335133</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101974</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet, ca 160 m NO om tjärnets norra ände, Dls</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>348563</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6519443</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Sumpskog med klibbal.</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335133</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>136097904</v>
+      </c>
+      <c r="B57" t="n">
+        <v>106433</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>348602</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6519311</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097904</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>136097886</v>
+      </c>
+      <c r="B58" t="n">
+        <v>102418</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>348812</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6519662</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097886</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>136097892</v>
+      </c>
+      <c r="B59" t="n">
+        <v>102418</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>348607</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6519437</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097892</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136097894</v>
+      </c>
+      <c r="B60" t="n">
+        <v>102418</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>348605</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6519385</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097894</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>136097901</v>
+      </c>
+      <c r="B61" t="n">
+        <v>102418</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>348632</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6519294</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097901</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>136097903</v>
+      </c>
+      <c r="B62" t="n">
+        <v>102418</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>348624</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6519288</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097903</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>136097913</v>
+      </c>
+      <c r="B63" t="n">
+        <v>102418</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>348537</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6519535</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097913</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>136097916</v>
+      </c>
+      <c r="B64" t="n">
+        <v>102418</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>348527</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6519500</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097916</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>136098084</v>
+      </c>
+      <c r="B65" t="n">
+        <v>102418</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>348668</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6519210</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136098084</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>136097902</v>
+      </c>
+      <c r="B66" t="n">
+        <v>104302</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221987</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Skogsbingel</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Mercurialis perennis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>348624</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6519288</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097902</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>121791393</v>
+      </c>
+      <c r="B67" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Janses kulle, Janses kulle, Dls</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>348597</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6519354</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121791393</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>132446006</v>
+      </c>
+      <c r="B68" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Janses kulle, Dls</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>348630</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6519376</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446006</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>132446030</v>
+      </c>
+      <c r="B69" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>348675</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6519199</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446030</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>132446073</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Skog söder om Lilla Skårsdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>348729</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6519685</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446073</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>136097895</v>
+      </c>
+      <c r="B71" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>348593</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6519392</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097895</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>136097917</v>
+      </c>
+      <c r="B72" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>348527</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6519500</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097917</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>136097919</v>
+      </c>
+      <c r="B73" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>348541</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6519474</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097919</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>136097920</v>
+      </c>
+      <c r="B74" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>348563</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6519496</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097920</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>136097940</v>
+      </c>
+      <c r="B75" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>348759</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6519595</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097940</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>136097945</v>
+      </c>
+      <c r="B76" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>348840</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6519584</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097945</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>136097888</v>
+      </c>
+      <c r="B77" t="n">
+        <v>101404</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>348854</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6519653</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097888</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>136097935</v>
+      </c>
+      <c r="B78" t="n">
+        <v>101404</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>348713</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6519667</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097935</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>136097937</v>
+      </c>
+      <c r="B79" t="n">
+        <v>101404</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>348713</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6519650</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097937</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>132446009</v>
+      </c>
+      <c r="B80" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Janses kulle, Dls</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>348626</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6519358</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446009</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>132446014</v>
+      </c>
+      <c r="B81" t="n">
+        <v>80403</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Janses kulle, Dls</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>348655</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6519352</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132446014</t>
         </is>
@@ -5108,6 +9313,46 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ81"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4365,10 +4365,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132446023</v>
+        <v>136101564</v>
       </c>
       <c r="B36" t="n">
-        <v>4776</v>
+        <v>92121</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4376,39 +4376,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100299</v>
+        <v>5321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>348665</v>
+        <v>348774</v>
       </c>
       <c r="R36" t="n">
-        <v>6519298</v>
+        <v>6519585</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4435,12 +4430,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4449,22 +4444,23 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4481,13 +4477,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446023</t>
+          <t>https://artportalen.se/Sighting/136101564</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132446079</v>
+        <v>132446023</v>
       </c>
       <c r="B37" t="n">
         <v>4776</v>
@@ -4523,14 +4519,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>348740</v>
+        <v>348665</v>
       </c>
       <c r="R37" t="n">
-        <v>6519761</v>
+        <v>6519298</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4603,16 +4599,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446079</t>
+          <t>https://artportalen.se/Sighting/132446023</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132446074</v>
+        <v>132446079</v>
       </c>
       <c r="B38" t="n">
-        <v>5181</v>
+        <v>4776</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4620,39 +4616,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>348747</v>
+        <v>348740</v>
       </c>
       <c r="R38" t="n">
-        <v>6519747</v>
+        <v>6519761</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4693,7 +4689,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4726,16 +4721,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446074</t>
+          <t>https://artportalen.se/Sighting/132446079</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136097897</v>
+        <v>132446074</v>
       </c>
       <c r="B39" t="n">
-        <v>5182</v>
+        <v>5181</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4761,21 +4756,21 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>348723</v>
+        <v>348747</v>
       </c>
       <c r="R39" t="n">
-        <v>6519121</v>
+        <v>6519747</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4802,12 +4797,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4816,6 +4811,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4848,16 +4844,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097897</t>
+          <t>https://artportalen.se/Sighting/132446074</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136097898</v>
+        <v>136097897</v>
       </c>
       <c r="B40" t="n">
-        <v>5202</v>
+        <v>5182</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4865,21 +4861,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4970,13 +4966,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097898</t>
+          <t>https://artportalen.se/Sighting/136097897</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136097942</v>
+        <v>136097898</v>
       </c>
       <c r="B41" t="n">
         <v>5202</v>
@@ -5016,10 +5012,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>348780</v>
+        <v>348723</v>
       </c>
       <c r="R41" t="n">
-        <v>6519577</v>
+        <v>6519121</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5092,38 +5088,38 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097942</t>
+          <t>https://artportalen.se/Sighting/136097898</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132445999</v>
+        <v>136097942</v>
       </c>
       <c r="B42" t="n">
-        <v>8374</v>
+        <v>5202</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106540</v>
+        <v>105930</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5134,14 +5130,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>348665</v>
+        <v>348780</v>
       </c>
       <c r="R42" t="n">
-        <v>6519431</v>
+        <v>6519577</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5168,12 +5164,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5187,17 +5183,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5214,13 +5210,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132445999</t>
+          <t>https://artportalen.se/Sighting/136097942</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132446029</v>
+        <v>132445999</v>
       </c>
       <c r="B43" t="n">
         <v>8374</v>
@@ -5256,14 +5252,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>348623</v>
+        <v>348665</v>
       </c>
       <c r="R43" t="n">
-        <v>6519241</v>
+        <v>6519431</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5336,51 +5332,56 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446029</t>
+          <t>https://artportalen.se/Sighting/132445999</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132446075</v>
+        <v>132446029</v>
       </c>
       <c r="B44" t="n">
-        <v>8449</v>
+        <v>8374</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106554</v>
+        <v>106540</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>348741</v>
+        <v>348623</v>
       </c>
       <c r="R44" t="n">
-        <v>6519743</v>
+        <v>6519241</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5424,6 +5425,21 @@
       <c r="AG44" t="b">
         <v>0</v>
       </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
@@ -5438,16 +5454,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446075</t>
+          <t>https://artportalen.se/Sighting/132446029</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136097896</v>
+        <v>132446075</v>
       </c>
       <c r="B45" t="n">
-        <v>8452</v>
+        <v>8449</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5473,21 +5489,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>348699</v>
+        <v>348741</v>
       </c>
       <c r="R45" t="n">
-        <v>6519187</v>
+        <v>6519743</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5514,12 +5525,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5545,51 +5556,56 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097896</t>
+          <t>https://artportalen.se/Sighting/132446075</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136097889</v>
+        <v>136097896</v>
       </c>
       <c r="B46" t="n">
-        <v>111586</v>
+        <v>8452</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219711</v>
+        <v>106554</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>348824</v>
+        <v>348699</v>
       </c>
       <c r="R46" t="n">
-        <v>6519586</v>
+        <v>6519187</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5647,13 +5663,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097889</t>
+          <t>https://artportalen.se/Sighting/136097896</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136097891</v>
+        <v>136097889</v>
       </c>
       <c r="B47" t="n">
         <v>111586</v>
@@ -5688,10 +5704,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>348614</v>
+        <v>348824</v>
       </c>
       <c r="R47" t="n">
-        <v>6519482</v>
+        <v>6519586</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5749,13 +5765,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097891</t>
+          <t>https://artportalen.se/Sighting/136097889</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136097893</v>
+        <v>136097891</v>
       </c>
       <c r="B48" t="n">
         <v>111586</v>
@@ -5790,10 +5806,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>348612</v>
+        <v>348614</v>
       </c>
       <c r="R48" t="n">
-        <v>6519392</v>
+        <v>6519482</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5851,13 +5867,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097893</t>
+          <t>https://artportalen.se/Sighting/136097891</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136097900</v>
+        <v>136097893</v>
       </c>
       <c r="B49" t="n">
         <v>111586</v>
@@ -5892,10 +5908,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>348618</v>
+        <v>348612</v>
       </c>
       <c r="R49" t="n">
-        <v>6519260</v>
+        <v>6519392</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5953,13 +5969,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097900</t>
+          <t>https://artportalen.se/Sighting/136097893</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136097921</v>
+        <v>136097900</v>
       </c>
       <c r="B50" t="n">
         <v>111586</v>
@@ -5994,10 +6010,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>348587</v>
+        <v>348618</v>
       </c>
       <c r="R50" t="n">
-        <v>6519511</v>
+        <v>6519260</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6055,13 +6071,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097921</t>
+          <t>https://artportalen.se/Sighting/136097900</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136097933</v>
+        <v>136097921</v>
       </c>
       <c r="B51" t="n">
         <v>111586</v>
@@ -6096,10 +6112,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>348673</v>
+        <v>348587</v>
       </c>
       <c r="R51" t="n">
-        <v>6519697</v>
+        <v>6519511</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6157,13 +6173,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097933</t>
+          <t>https://artportalen.se/Sighting/136097921</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136097936</v>
+        <v>136097933</v>
       </c>
       <c r="B52" t="n">
         <v>111586</v>
@@ -6198,10 +6214,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>348711</v>
+        <v>348673</v>
       </c>
       <c r="R52" t="n">
-        <v>6519665</v>
+        <v>6519697</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6259,13 +6275,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097936</t>
+          <t>https://artportalen.se/Sighting/136097933</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136097939</v>
+        <v>136097936</v>
       </c>
       <c r="B53" t="n">
         <v>111586</v>
@@ -6300,10 +6316,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>348745</v>
+        <v>348711</v>
       </c>
       <c r="R53" t="n">
-        <v>6519603</v>
+        <v>6519665</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6361,13 +6377,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097939</t>
+          <t>https://artportalen.se/Sighting/136097936</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136097943</v>
+        <v>136097939</v>
       </c>
       <c r="B54" t="n">
         <v>111586</v>
@@ -6402,10 +6418,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>348818</v>
+        <v>348745</v>
       </c>
       <c r="R54" t="n">
-        <v>6519588</v>
+        <v>6519603</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6463,13 +6479,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097943</t>
+          <t>https://artportalen.se/Sighting/136097939</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136097946</v>
+        <v>136097943</v>
       </c>
       <c r="B55" t="n">
         <v>111586</v>
@@ -6504,10 +6520,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>348846</v>
+        <v>348818</v>
       </c>
       <c r="R55" t="n">
-        <v>6519619</v>
+        <v>6519588</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6565,16 +6581,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097946</t>
+          <t>https://artportalen.se/Sighting/136097943</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132335133</v>
+        <v>136097946</v>
       </c>
       <c r="B56" t="n">
-        <v>101974</v>
+        <v>111586</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6582,16 +6598,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220075</v>
+        <v>219711</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chrysosplenium alternifolium</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6602,17 +6618,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, ca 160 m NO om tjärnets norra ände, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>348563</v>
+        <v>348846</v>
       </c>
       <c r="R56" t="n">
-        <v>6519443</v>
+        <v>6519619</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6636,12 +6652,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6652,74 +6668,69 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Sumpskog med klibbal.</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335133</t>
+          <t>https://artportalen.se/Sighting/136097946</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136097904</v>
+        <v>132335133</v>
       </c>
       <c r="B57" t="n">
-        <v>106433</v>
+        <v>101974</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>220075</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Vandringstjärnet, ca 160 m NO om tjärnets norra ände, Dls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>348602</v>
+        <v>348563</v>
       </c>
       <c r="R57" t="n">
-        <v>6519311</v>
+        <v>6519443</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6743,12 +6754,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6759,53 +6770,58 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Sumpskog med klibbal.</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097904</t>
+          <t>https://artportalen.se/Sighting/132335133</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136097886</v>
+        <v>136097904</v>
       </c>
       <c r="B58" t="n">
-        <v>102418</v>
+        <v>106433</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6815,10 +6831,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>348812</v>
+        <v>348602</v>
       </c>
       <c r="R58" t="n">
-        <v>6519662</v>
+        <v>6519311</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6876,13 +6892,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097886</t>
+          <t>https://artportalen.se/Sighting/136097904</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136097892</v>
+        <v>136097886</v>
       </c>
       <c r="B59" t="n">
         <v>102418</v>
@@ -6917,10 +6933,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>348607</v>
+        <v>348812</v>
       </c>
       <c r="R59" t="n">
-        <v>6519437</v>
+        <v>6519662</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6978,13 +6994,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097892</t>
+          <t>https://artportalen.se/Sighting/136097886</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136097894</v>
+        <v>136097892</v>
       </c>
       <c r="B60" t="n">
         <v>102418</v>
@@ -7019,10 +7035,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>348605</v>
+        <v>348607</v>
       </c>
       <c r="R60" t="n">
-        <v>6519385</v>
+        <v>6519437</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7080,13 +7096,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097894</t>
+          <t>https://artportalen.se/Sighting/136097892</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136097901</v>
+        <v>136097894</v>
       </c>
       <c r="B61" t="n">
         <v>102418</v>
@@ -7121,10 +7137,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>348632</v>
+        <v>348605</v>
       </c>
       <c r="R61" t="n">
-        <v>6519294</v>
+        <v>6519385</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7182,13 +7198,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097901</t>
+          <t>https://artportalen.se/Sighting/136097894</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136097903</v>
+        <v>136097901</v>
       </c>
       <c r="B62" t="n">
         <v>102418</v>
@@ -7223,10 +7239,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>348624</v>
+        <v>348632</v>
       </c>
       <c r="R62" t="n">
-        <v>6519288</v>
+        <v>6519294</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7284,13 +7300,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097903</t>
+          <t>https://artportalen.se/Sighting/136097901</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136097913</v>
+        <v>136097903</v>
       </c>
       <c r="B63" t="n">
         <v>102418</v>
@@ -7325,10 +7341,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>348537</v>
+        <v>348624</v>
       </c>
       <c r="R63" t="n">
-        <v>6519535</v>
+        <v>6519288</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7386,13 +7402,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097913</t>
+          <t>https://artportalen.se/Sighting/136097903</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136097916</v>
+        <v>136097913</v>
       </c>
       <c r="B64" t="n">
         <v>102418</v>
@@ -7427,10 +7443,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>348527</v>
+        <v>348537</v>
       </c>
       <c r="R64" t="n">
-        <v>6519500</v>
+        <v>6519535</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7488,13 +7504,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097916</t>
+          <t>https://artportalen.se/Sighting/136097913</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136098084</v>
+        <v>136097916</v>
       </c>
       <c r="B65" t="n">
         <v>102418</v>
@@ -7529,10 +7545,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>348668</v>
+        <v>348527</v>
       </c>
       <c r="R65" t="n">
-        <v>6519210</v>
+        <v>6519500</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7590,38 +7606,38 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136098084</t>
+          <t>https://artportalen.se/Sighting/136097916</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136097902</v>
+        <v>136098084</v>
       </c>
       <c r="B66" t="n">
-        <v>104302</v>
+        <v>102418</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221987</v>
+        <v>221235</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsbingel</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Mercurialis perennis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7631,10 +7647,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>348624</v>
+        <v>348668</v>
       </c>
       <c r="R66" t="n">
-        <v>6519288</v>
+        <v>6519210</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7692,16 +7708,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097902</t>
+          <t>https://artportalen.se/Sighting/136098084</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121791393</v>
+        <v>136097902</v>
       </c>
       <c r="B67" t="n">
-        <v>101326</v>
+        <v>104302</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7709,47 +7725,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>221987</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsbingel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Mercurialis perennis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>348597</v>
+        <v>348624</v>
       </c>
       <c r="R67" t="n">
-        <v>6519354</v>
+        <v>6519288</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7773,12 +7779,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7789,36 +7795,31 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121791393</t>
+          <t>https://artportalen.se/Sighting/136097902</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132446006</v>
+        <v>121791393</v>
       </c>
       <c r="B68" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7844,19 +7845,29 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>348630</v>
+        <v>348597</v>
       </c>
       <c r="R68" t="n">
-        <v>6519376</v>
+        <v>6519354</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7880,12 +7891,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7896,28 +7907,33 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446006</t>
+          <t>https://artportalen.se/Sighting/121791393</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132446030</v>
+        <v>132446006</v>
       </c>
       <c r="B69" t="n">
         <v>101403</v>
@@ -7948,14 +7964,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>348675</v>
+        <v>348630</v>
       </c>
       <c r="R69" t="n">
-        <v>6519199</v>
+        <v>6519376</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8013,13 +8029,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446030</t>
+          <t>https://artportalen.se/Sighting/132446006</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132446073</v>
+        <v>132446030</v>
       </c>
       <c r="B70" t="n">
         <v>101403</v>
@@ -8050,14 +8066,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skog söder om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>348729</v>
+        <v>348675</v>
       </c>
       <c r="R70" t="n">
-        <v>6519685</v>
+        <v>6519199</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8115,16 +8131,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446073</t>
+          <t>https://artportalen.se/Sighting/132446030</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136097895</v>
+        <v>132446073</v>
       </c>
       <c r="B71" t="n">
-        <v>101502</v>
+        <v>101403</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8152,14 +8168,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skog söder om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>348593</v>
+        <v>348729</v>
       </c>
       <c r="R71" t="n">
-        <v>6519392</v>
+        <v>6519685</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8186,12 +8202,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8217,13 +8233,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097895</t>
+          <t>https://artportalen.se/Sighting/132446073</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>136097917</v>
+        <v>136097895</v>
       </c>
       <c r="B72" t="n">
         <v>101502</v>
@@ -8258,10 +8274,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>348527</v>
+        <v>348593</v>
       </c>
       <c r="R72" t="n">
-        <v>6519500</v>
+        <v>6519392</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8319,13 +8335,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097917</t>
+          <t>https://artportalen.se/Sighting/136097895</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>136097919</v>
+        <v>136097917</v>
       </c>
       <c r="B73" t="n">
         <v>101502</v>
@@ -8360,10 +8376,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>348541</v>
+        <v>348527</v>
       </c>
       <c r="R73" t="n">
-        <v>6519474</v>
+        <v>6519500</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8421,13 +8437,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097919</t>
+          <t>https://artportalen.se/Sighting/136097917</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>136097920</v>
+        <v>136097919</v>
       </c>
       <c r="B74" t="n">
         <v>101502</v>
@@ -8462,10 +8478,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>348563</v>
+        <v>348541</v>
       </c>
       <c r="R74" t="n">
-        <v>6519496</v>
+        <v>6519474</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8523,13 +8539,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097920</t>
+          <t>https://artportalen.se/Sighting/136097919</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>136097940</v>
+        <v>136097920</v>
       </c>
       <c r="B75" t="n">
         <v>101502</v>
@@ -8564,10 +8580,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>348759</v>
+        <v>348563</v>
       </c>
       <c r="R75" t="n">
-        <v>6519595</v>
+        <v>6519496</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8625,13 +8641,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097940</t>
+          <t>https://artportalen.se/Sighting/136097920</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>136097945</v>
+        <v>136097940</v>
       </c>
       <c r="B76" t="n">
         <v>101502</v>
@@ -8666,10 +8682,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>348840</v>
+        <v>348759</v>
       </c>
       <c r="R76" t="n">
-        <v>6519584</v>
+        <v>6519595</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8727,16 +8743,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097945</t>
+          <t>https://artportalen.se/Sighting/136097940</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136097888</v>
+        <v>136097945</v>
       </c>
       <c r="B77" t="n">
-        <v>101404</v>
+        <v>101502</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8744,21 +8760,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8768,10 +8784,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>348854</v>
+        <v>348840</v>
       </c>
       <c r="R77" t="n">
-        <v>6519653</v>
+        <v>6519584</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8829,13 +8845,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097888</t>
+          <t>https://artportalen.se/Sighting/136097945</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136097935</v>
+        <v>136097888</v>
       </c>
       <c r="B78" t="n">
         <v>101404</v>
@@ -8870,10 +8886,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>348713</v>
+        <v>348854</v>
       </c>
       <c r="R78" t="n">
-        <v>6519667</v>
+        <v>6519653</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8931,13 +8947,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097935</t>
+          <t>https://artportalen.se/Sighting/136097888</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>136097937</v>
+        <v>136097935</v>
       </c>
       <c r="B79" t="n">
         <v>101404</v>
@@ -8975,7 +8991,7 @@
         <v>348713</v>
       </c>
       <c r="R79" t="n">
-        <v>6519650</v>
+        <v>6519667</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9033,16 +9049,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097937</t>
+          <t>https://artportalen.se/Sighting/136097935</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132446009</v>
+        <v>136097937</v>
       </c>
       <c r="B80" t="n">
-        <v>80438</v>
+        <v>101404</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9050,34 +9066,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229497</v>
+        <v>222771</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>348626</v>
+        <v>348713</v>
       </c>
       <c r="R80" t="n">
-        <v>6519358</v>
+        <v>6519650</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9104,12 +9120,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9120,21 +9136,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9150,16 +9151,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446009</t>
+          <t>https://artportalen.se/Sighting/136097937</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132446014</v>
+        <v>132446009</v>
       </c>
       <c r="B81" t="n">
-        <v>80403</v>
+        <v>80438</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9167,21 +9168,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003719</v>
+        <v>229497</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9191,10 +9192,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>348655</v>
+        <v>348626</v>
       </c>
       <c r="R81" t="n">
-        <v>6519352</v>
+        <v>6519358</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9266,6 +9267,123 @@
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446009</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>132446014</v>
+      </c>
+      <c r="B82" t="n">
+        <v>80403</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Janses kulle, Dls</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>348655</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6519352</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132446014</t>
         </is>
@@ -9353,6 +9471,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2103,7 +2103,7 @@
         <v>136097908</v>
       </c>
       <c r="B15" t="n">
-        <v>96607</v>
+        <v>96608</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136097912</v>
       </c>
       <c r="B16" t="n">
-        <v>96607</v>
+        <v>96608</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136097911</v>
       </c>
       <c r="B22" t="n">
-        <v>96356</v>
+        <v>96357</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136097914</v>
       </c>
       <c r="B27" t="n">
-        <v>96401</v>
+        <v>96402</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96628</v>
+        <v>96629</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96628</v>
+        <v>96629</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96628</v>
+        <v>96629</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136101564</v>
       </c>
       <c r="B36" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>136097889</v>
       </c>
       <c r="B47" t="n">
-        <v>111586</v>
+        <v>111588</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>136097891</v>
       </c>
       <c r="B48" t="n">
-        <v>111586</v>
+        <v>111588</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136097893</v>
       </c>
       <c r="B49" t="n">
-        <v>111586</v>
+        <v>111588</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136097900</v>
       </c>
       <c r="B50" t="n">
-        <v>111586</v>
+        <v>111588</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136097921</v>
       </c>
       <c r="B51" t="n">
-        <v>111586</v>
+        <v>111588</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136097933</v>
       </c>
       <c r="B52" t="n">
-        <v>111586</v>
+        <v>111588</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>136097936</v>
       </c>
       <c r="B53" t="n">
-        <v>111586</v>
+        <v>111588</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>136097939</v>
       </c>
       <c r="B54" t="n">
-        <v>111586</v>
+        <v>111588</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136097943</v>
       </c>
       <c r="B55" t="n">
-        <v>111586</v>
+        <v>111588</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136097946</v>
       </c>
       <c r="B56" t="n">
-        <v>111586</v>
+        <v>111588</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>136097904</v>
       </c>
       <c r="B58" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>136097886</v>
       </c>
       <c r="B59" t="n">
-        <v>102418</v>
+        <v>102420</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136097892</v>
       </c>
       <c r="B60" t="n">
-        <v>102418</v>
+        <v>102420</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136097894</v>
       </c>
       <c r="B61" t="n">
-        <v>102418</v>
+        <v>102420</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136097901</v>
       </c>
       <c r="B62" t="n">
-        <v>102418</v>
+        <v>102420</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>136097903</v>
       </c>
       <c r="B63" t="n">
-        <v>102418</v>
+        <v>102420</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>136097913</v>
       </c>
       <c r="B64" t="n">
-        <v>102418</v>
+        <v>102420</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>136097916</v>
       </c>
       <c r="B65" t="n">
-        <v>102418</v>
+        <v>102420</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>136098084</v>
       </c>
       <c r="B66" t="n">
-        <v>102418</v>
+        <v>102420</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>136097902</v>
       </c>
       <c r="B67" t="n">
-        <v>104302</v>
+        <v>104304</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>136097895</v>
       </c>
       <c r="B72" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136097917</v>
       </c>
       <c r="B73" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>136097919</v>
       </c>
       <c r="B74" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136097920</v>
       </c>
       <c r="B75" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>136097940</v>
       </c>
       <c r="B76" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136097945</v>
       </c>
       <c r="B77" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>136097888</v>
       </c>
       <c r="B78" t="n">
-        <v>101404</v>
+        <v>101406</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136097935</v>
       </c>
       <c r="B79" t="n">
-        <v>101404</v>
+        <v>101406</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>136097937</v>
       </c>
       <c r="B80" t="n">
-        <v>101404</v>
+        <v>101406</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2103,7 +2103,7 @@
         <v>136097908</v>
       </c>
       <c r="B15" t="n">
-        <v>96608</v>
+        <v>96609</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136097912</v>
       </c>
       <c r="B16" t="n">
-        <v>96608</v>
+        <v>96609</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136097911</v>
       </c>
       <c r="B22" t="n">
-        <v>96357</v>
+        <v>96358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136097914</v>
       </c>
       <c r="B27" t="n">
-        <v>96402</v>
+        <v>96403</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136101564</v>
       </c>
       <c r="B36" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>136097889</v>
       </c>
       <c r="B47" t="n">
-        <v>111588</v>
+        <v>111589</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>136097891</v>
       </c>
       <c r="B48" t="n">
-        <v>111588</v>
+        <v>111589</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136097893</v>
       </c>
       <c r="B49" t="n">
-        <v>111588</v>
+        <v>111589</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136097900</v>
       </c>
       <c r="B50" t="n">
-        <v>111588</v>
+        <v>111589</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136097921</v>
       </c>
       <c r="B51" t="n">
-        <v>111588</v>
+        <v>111589</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136097933</v>
       </c>
       <c r="B52" t="n">
-        <v>111588</v>
+        <v>111589</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>136097936</v>
       </c>
       <c r="B53" t="n">
-        <v>111588</v>
+        <v>111589</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>136097939</v>
       </c>
       <c r="B54" t="n">
-        <v>111588</v>
+        <v>111589</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136097943</v>
       </c>
       <c r="B55" t="n">
-        <v>111588</v>
+        <v>111589</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136097946</v>
       </c>
       <c r="B56" t="n">
-        <v>111588</v>
+        <v>111589</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>136097904</v>
       </c>
       <c r="B58" t="n">
-        <v>106435</v>
+        <v>106436</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>136097886</v>
       </c>
       <c r="B59" t="n">
-        <v>102420</v>
+        <v>102421</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136097892</v>
       </c>
       <c r="B60" t="n">
-        <v>102420</v>
+        <v>102421</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136097894</v>
       </c>
       <c r="B61" t="n">
-        <v>102420</v>
+        <v>102421</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136097901</v>
       </c>
       <c r="B62" t="n">
-        <v>102420</v>
+        <v>102421</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>136097903</v>
       </c>
       <c r="B63" t="n">
-        <v>102420</v>
+        <v>102421</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>136097913</v>
       </c>
       <c r="B64" t="n">
-        <v>102420</v>
+        <v>102421</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>136097916</v>
       </c>
       <c r="B65" t="n">
-        <v>102420</v>
+        <v>102421</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>136098084</v>
       </c>
       <c r="B66" t="n">
-        <v>102420</v>
+        <v>102421</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>136097902</v>
       </c>
       <c r="B67" t="n">
-        <v>104304</v>
+        <v>104305</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>136097895</v>
       </c>
       <c r="B72" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136097917</v>
       </c>
       <c r="B73" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>136097919</v>
       </c>
       <c r="B74" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136097920</v>
       </c>
       <c r="B75" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>136097940</v>
       </c>
       <c r="B76" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136097945</v>
       </c>
       <c r="B77" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>136097888</v>
       </c>
       <c r="B78" t="n">
-        <v>101406</v>
+        <v>101407</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136097935</v>
       </c>
       <c r="B79" t="n">
-        <v>101406</v>
+        <v>101407</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>136097937</v>
       </c>
       <c r="B80" t="n">
-        <v>101406</v>
+        <v>101407</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2103,7 +2103,7 @@
         <v>136097908</v>
       </c>
       <c r="B15" t="n">
-        <v>96609</v>
+        <v>96610</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136097912</v>
       </c>
       <c r="B16" t="n">
-        <v>96609</v>
+        <v>96610</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136097911</v>
       </c>
       <c r="B22" t="n">
-        <v>96358</v>
+        <v>96359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136097914</v>
       </c>
       <c r="B27" t="n">
-        <v>96403</v>
+        <v>96404</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136101564</v>
       </c>
       <c r="B36" t="n">
-        <v>92123</v>
+        <v>92124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>136097889</v>
       </c>
       <c r="B47" t="n">
-        <v>111589</v>
+        <v>111590</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>136097891</v>
       </c>
       <c r="B48" t="n">
-        <v>111589</v>
+        <v>111590</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136097893</v>
       </c>
       <c r="B49" t="n">
-        <v>111589</v>
+        <v>111590</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136097900</v>
       </c>
       <c r="B50" t="n">
-        <v>111589</v>
+        <v>111590</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136097921</v>
       </c>
       <c r="B51" t="n">
-        <v>111589</v>
+        <v>111590</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136097933</v>
       </c>
       <c r="B52" t="n">
-        <v>111589</v>
+        <v>111590</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>136097936</v>
       </c>
       <c r="B53" t="n">
-        <v>111589</v>
+        <v>111590</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>136097939</v>
       </c>
       <c r="B54" t="n">
-        <v>111589</v>
+        <v>111590</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136097943</v>
       </c>
       <c r="B55" t="n">
-        <v>111589</v>
+        <v>111590</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136097946</v>
       </c>
       <c r="B56" t="n">
-        <v>111589</v>
+        <v>111590</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>136097904</v>
       </c>
       <c r="B58" t="n">
-        <v>106436</v>
+        <v>106437</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>136097886</v>
       </c>
       <c r="B59" t="n">
-        <v>102421</v>
+        <v>102422</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136097892</v>
       </c>
       <c r="B60" t="n">
-        <v>102421</v>
+        <v>102422</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136097894</v>
       </c>
       <c r="B61" t="n">
-        <v>102421</v>
+        <v>102422</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136097901</v>
       </c>
       <c r="B62" t="n">
-        <v>102421</v>
+        <v>102422</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>136097903</v>
       </c>
       <c r="B63" t="n">
-        <v>102421</v>
+        <v>102422</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>136097913</v>
       </c>
       <c r="B64" t="n">
-        <v>102421</v>
+        <v>102422</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>136097916</v>
       </c>
       <c r="B65" t="n">
-        <v>102421</v>
+        <v>102422</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>136098084</v>
       </c>
       <c r="B66" t="n">
-        <v>102421</v>
+        <v>102422</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>136097902</v>
       </c>
       <c r="B67" t="n">
-        <v>104305</v>
+        <v>104306</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>136097895</v>
       </c>
       <c r="B72" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136097917</v>
       </c>
       <c r="B73" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>136097919</v>
       </c>
       <c r="B74" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136097920</v>
       </c>
       <c r="B75" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>136097940</v>
       </c>
       <c r="B76" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136097945</v>
       </c>
       <c r="B77" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>136097888</v>
       </c>
       <c r="B78" t="n">
-        <v>101407</v>
+        <v>101408</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136097935</v>
       </c>
       <c r="B79" t="n">
-        <v>101407</v>
+        <v>101408</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>136097937</v>
       </c>
       <c r="B80" t="n">
-        <v>101407</v>
+        <v>101408</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2103,7 +2103,7 @@
         <v>136097908</v>
       </c>
       <c r="B15" t="n">
-        <v>96610</v>
+        <v>96616</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136097912</v>
       </c>
       <c r="B16" t="n">
-        <v>96610</v>
+        <v>96616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136097911</v>
       </c>
       <c r="B22" t="n">
-        <v>96359</v>
+        <v>96365</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136097914</v>
       </c>
       <c r="B27" t="n">
-        <v>96404</v>
+        <v>96410</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96631</v>
+        <v>96637</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96631</v>
+        <v>96637</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96631</v>
+        <v>96637</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136101564</v>
       </c>
       <c r="B36" t="n">
-        <v>92124</v>
+        <v>92130</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>136097889</v>
       </c>
       <c r="B47" t="n">
-        <v>111590</v>
+        <v>111596</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>136097891</v>
       </c>
       <c r="B48" t="n">
-        <v>111590</v>
+        <v>111596</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136097893</v>
       </c>
       <c r="B49" t="n">
-        <v>111590</v>
+        <v>111596</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136097900</v>
       </c>
       <c r="B50" t="n">
-        <v>111590</v>
+        <v>111596</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136097921</v>
       </c>
       <c r="B51" t="n">
-        <v>111590</v>
+        <v>111596</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136097933</v>
       </c>
       <c r="B52" t="n">
-        <v>111590</v>
+        <v>111596</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>136097936</v>
       </c>
       <c r="B53" t="n">
-        <v>111590</v>
+        <v>111596</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>136097939</v>
       </c>
       <c r="B54" t="n">
-        <v>111590</v>
+        <v>111596</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136097943</v>
       </c>
       <c r="B55" t="n">
-        <v>111590</v>
+        <v>111596</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136097946</v>
       </c>
       <c r="B56" t="n">
-        <v>111590</v>
+        <v>111596</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>136097904</v>
       </c>
       <c r="B58" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>136097886</v>
       </c>
       <c r="B59" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136097892</v>
       </c>
       <c r="B60" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136097894</v>
       </c>
       <c r="B61" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136097901</v>
       </c>
       <c r="B62" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>136097903</v>
       </c>
       <c r="B63" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>136097913</v>
       </c>
       <c r="B64" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>136097916</v>
       </c>
       <c r="B65" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>136098084</v>
       </c>
       <c r="B66" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>136097902</v>
       </c>
       <c r="B67" t="n">
-        <v>104306</v>
+        <v>104312</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>136097895</v>
       </c>
       <c r="B72" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136097917</v>
       </c>
       <c r="B73" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>136097919</v>
       </c>
       <c r="B74" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136097920</v>
       </c>
       <c r="B75" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>136097940</v>
       </c>
       <c r="B76" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136097945</v>
       </c>
       <c r="B77" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>136097888</v>
       </c>
       <c r="B78" t="n">
-        <v>101408</v>
+        <v>101414</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136097935</v>
       </c>
       <c r="B79" t="n">
-        <v>101408</v>
+        <v>101414</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>136097937</v>
       </c>
       <c r="B80" t="n">
-        <v>101408</v>
+        <v>101414</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2103,7 +2103,7 @@
         <v>136097908</v>
       </c>
       <c r="B15" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136097912</v>
       </c>
       <c r="B16" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136097911</v>
       </c>
       <c r="B22" t="n">
-        <v>96365</v>
+        <v>96366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136097914</v>
       </c>
       <c r="B27" t="n">
-        <v>96410</v>
+        <v>96411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96637</v>
+        <v>96638</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96637</v>
+        <v>96638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96637</v>
+        <v>96638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136101564</v>
       </c>
       <c r="B36" t="n">
-        <v>92130</v>
+        <v>92131</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>136097889</v>
       </c>
       <c r="B47" t="n">
-        <v>111596</v>
+        <v>111597</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>136097891</v>
       </c>
       <c r="B48" t="n">
-        <v>111596</v>
+        <v>111597</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136097893</v>
       </c>
       <c r="B49" t="n">
-        <v>111596</v>
+        <v>111597</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136097900</v>
       </c>
       <c r="B50" t="n">
-        <v>111596</v>
+        <v>111597</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136097921</v>
       </c>
       <c r="B51" t="n">
-        <v>111596</v>
+        <v>111597</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136097933</v>
       </c>
       <c r="B52" t="n">
-        <v>111596</v>
+        <v>111597</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>136097936</v>
       </c>
       <c r="B53" t="n">
-        <v>111596</v>
+        <v>111597</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>136097939</v>
       </c>
       <c r="B54" t="n">
-        <v>111596</v>
+        <v>111597</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136097943</v>
       </c>
       <c r="B55" t="n">
-        <v>111596</v>
+        <v>111597</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136097946</v>
       </c>
       <c r="B56" t="n">
-        <v>111596</v>
+        <v>111597</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>136097904</v>
       </c>
       <c r="B58" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>136097886</v>
       </c>
       <c r="B59" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136097892</v>
       </c>
       <c r="B60" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136097894</v>
       </c>
       <c r="B61" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136097901</v>
       </c>
       <c r="B62" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>136097903</v>
       </c>
       <c r="B63" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>136097913</v>
       </c>
       <c r="B64" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>136097916</v>
       </c>
       <c r="B65" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>136098084</v>
       </c>
       <c r="B66" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>136097902</v>
       </c>
       <c r="B67" t="n">
-        <v>104312</v>
+        <v>104313</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>136097895</v>
       </c>
       <c r="B72" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136097917</v>
       </c>
       <c r="B73" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>136097919</v>
       </c>
       <c r="B74" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136097920</v>
       </c>
       <c r="B75" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>136097940</v>
       </c>
       <c r="B76" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136097945</v>
       </c>
       <c r="B77" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>136097888</v>
       </c>
       <c r="B78" t="n">
-        <v>101414</v>
+        <v>101415</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136097935</v>
       </c>
       <c r="B79" t="n">
-        <v>101414</v>
+        <v>101415</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>136097937</v>
       </c>
       <c r="B80" t="n">
-        <v>101414</v>
+        <v>101415</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2103,7 +2103,7 @@
         <v>136097908</v>
       </c>
       <c r="B15" t="n">
-        <v>96617</v>
+        <v>96628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136097912</v>
       </c>
       <c r="B16" t="n">
-        <v>96617</v>
+        <v>96628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136097911</v>
       </c>
       <c r="B22" t="n">
-        <v>96366</v>
+        <v>96377</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136097914</v>
       </c>
       <c r="B27" t="n">
-        <v>96411</v>
+        <v>96422</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96638</v>
+        <v>96649</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96638</v>
+        <v>96649</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96638</v>
+        <v>96649</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136101564</v>
       </c>
       <c r="B36" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>136097889</v>
       </c>
       <c r="B47" t="n">
-        <v>111597</v>
+        <v>111608</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>136097891</v>
       </c>
       <c r="B48" t="n">
-        <v>111597</v>
+        <v>111608</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136097893</v>
       </c>
       <c r="B49" t="n">
-        <v>111597</v>
+        <v>111608</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136097900</v>
       </c>
       <c r="B50" t="n">
-        <v>111597</v>
+        <v>111608</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136097921</v>
       </c>
       <c r="B51" t="n">
-        <v>111597</v>
+        <v>111608</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136097933</v>
       </c>
       <c r="B52" t="n">
-        <v>111597</v>
+        <v>111608</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>136097936</v>
       </c>
       <c r="B53" t="n">
-        <v>111597</v>
+        <v>111608</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>136097939</v>
       </c>
       <c r="B54" t="n">
-        <v>111597</v>
+        <v>111608</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136097943</v>
       </c>
       <c r="B55" t="n">
-        <v>111597</v>
+        <v>111608</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136097946</v>
       </c>
       <c r="B56" t="n">
-        <v>111597</v>
+        <v>111608</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>136097904</v>
       </c>
       <c r="B58" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>136097886</v>
       </c>
       <c r="B59" t="n">
-        <v>102429</v>
+        <v>102440</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136097892</v>
       </c>
       <c r="B60" t="n">
-        <v>102429</v>
+        <v>102440</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136097894</v>
       </c>
       <c r="B61" t="n">
-        <v>102429</v>
+        <v>102440</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136097901</v>
       </c>
       <c r="B62" t="n">
-        <v>102429</v>
+        <v>102440</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>136097903</v>
       </c>
       <c r="B63" t="n">
-        <v>102429</v>
+        <v>102440</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>136097913</v>
       </c>
       <c r="B64" t="n">
-        <v>102429</v>
+        <v>102440</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>136097916</v>
       </c>
       <c r="B65" t="n">
-        <v>102429</v>
+        <v>102440</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>136098084</v>
       </c>
       <c r="B66" t="n">
-        <v>102429</v>
+        <v>102440</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>136097902</v>
       </c>
       <c r="B67" t="n">
-        <v>104313</v>
+        <v>104324</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>136097895</v>
       </c>
       <c r="B72" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136097917</v>
       </c>
       <c r="B73" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>136097919</v>
       </c>
       <c r="B74" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136097920</v>
       </c>
       <c r="B75" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>136097940</v>
       </c>
       <c r="B76" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136097945</v>
       </c>
       <c r="B77" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>136097888</v>
       </c>
       <c r="B78" t="n">
-        <v>101415</v>
+        <v>101426</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136097935</v>
       </c>
       <c r="B79" t="n">
-        <v>101415</v>
+        <v>101426</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>136097937</v>
       </c>
       <c r="B80" t="n">
-        <v>101415</v>
+        <v>101426</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2103,7 +2103,7 @@
         <v>136097908</v>
       </c>
       <c r="B15" t="n">
-        <v>96628</v>
+        <v>96641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136097912</v>
       </c>
       <c r="B16" t="n">
-        <v>96628</v>
+        <v>96641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136097911</v>
       </c>
       <c r="B22" t="n">
-        <v>96377</v>
+        <v>96390</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136097914</v>
       </c>
       <c r="B27" t="n">
-        <v>96422</v>
+        <v>96435</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96649</v>
+        <v>96662</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96649</v>
+        <v>96662</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96649</v>
+        <v>96662</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136101564</v>
       </c>
       <c r="B36" t="n">
-        <v>92137</v>
+        <v>92144</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>136097889</v>
       </c>
       <c r="B47" t="n">
-        <v>111608</v>
+        <v>111621</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>136097891</v>
       </c>
       <c r="B48" t="n">
-        <v>111608</v>
+        <v>111621</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136097893</v>
       </c>
       <c r="B49" t="n">
-        <v>111608</v>
+        <v>111621</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136097900</v>
       </c>
       <c r="B50" t="n">
-        <v>111608</v>
+        <v>111621</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136097921</v>
       </c>
       <c r="B51" t="n">
-        <v>111608</v>
+        <v>111621</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136097933</v>
       </c>
       <c r="B52" t="n">
-        <v>111608</v>
+        <v>111621</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>136097936</v>
       </c>
       <c r="B53" t="n">
-        <v>111608</v>
+        <v>111621</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>136097939</v>
       </c>
       <c r="B54" t="n">
-        <v>111608</v>
+        <v>111621</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136097943</v>
       </c>
       <c r="B55" t="n">
-        <v>111608</v>
+        <v>111621</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136097946</v>
       </c>
       <c r="B56" t="n">
-        <v>111608</v>
+        <v>111621</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>136097904</v>
       </c>
       <c r="B58" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>136097886</v>
       </c>
       <c r="B59" t="n">
-        <v>102440</v>
+        <v>102453</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136097892</v>
       </c>
       <c r="B60" t="n">
-        <v>102440</v>
+        <v>102453</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136097894</v>
       </c>
       <c r="B61" t="n">
-        <v>102440</v>
+        <v>102453</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136097901</v>
       </c>
       <c r="B62" t="n">
-        <v>102440</v>
+        <v>102453</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>136097903</v>
       </c>
       <c r="B63" t="n">
-        <v>102440</v>
+        <v>102453</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>136097913</v>
       </c>
       <c r="B64" t="n">
-        <v>102440</v>
+        <v>102453</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>136097916</v>
       </c>
       <c r="B65" t="n">
-        <v>102440</v>
+        <v>102453</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>136098084</v>
       </c>
       <c r="B66" t="n">
-        <v>102440</v>
+        <v>102453</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>136097902</v>
       </c>
       <c r="B67" t="n">
-        <v>104324</v>
+        <v>104337</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>136097895</v>
       </c>
       <c r="B72" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136097917</v>
       </c>
       <c r="B73" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>136097919</v>
       </c>
       <c r="B74" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136097920</v>
       </c>
       <c r="B75" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>136097940</v>
       </c>
       <c r="B76" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136097945</v>
       </c>
       <c r="B77" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>136097888</v>
       </c>
       <c r="B78" t="n">
-        <v>101426</v>
+        <v>101439</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136097935</v>
       </c>
       <c r="B79" t="n">
-        <v>101426</v>
+        <v>101439</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>136097937</v>
       </c>
       <c r="B80" t="n">
-        <v>101426</v>
+        <v>101439</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2103,7 +2103,7 @@
         <v>136097908</v>
       </c>
       <c r="B15" t="n">
-        <v>96641</v>
+        <v>96642</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136097912</v>
       </c>
       <c r="B16" t="n">
-        <v>96641</v>
+        <v>96642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136097911</v>
       </c>
       <c r="B22" t="n">
-        <v>96390</v>
+        <v>96391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136097914</v>
       </c>
       <c r="B27" t="n">
-        <v>96435</v>
+        <v>96436</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96662</v>
+        <v>96663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96662</v>
+        <v>96663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96662</v>
+        <v>96663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136101564</v>
       </c>
       <c r="B36" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>136097889</v>
       </c>
       <c r="B47" t="n">
-        <v>111621</v>
+        <v>111622</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>136097891</v>
       </c>
       <c r="B48" t="n">
-        <v>111621</v>
+        <v>111622</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136097893</v>
       </c>
       <c r="B49" t="n">
-        <v>111621</v>
+        <v>111622</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136097900</v>
       </c>
       <c r="B50" t="n">
-        <v>111621</v>
+        <v>111622</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136097921</v>
       </c>
       <c r="B51" t="n">
-        <v>111621</v>
+        <v>111622</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136097933</v>
       </c>
       <c r="B52" t="n">
-        <v>111621</v>
+        <v>111622</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>136097936</v>
       </c>
       <c r="B53" t="n">
-        <v>111621</v>
+        <v>111622</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>136097939</v>
       </c>
       <c r="B54" t="n">
-        <v>111621</v>
+        <v>111622</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136097943</v>
       </c>
       <c r="B55" t="n">
-        <v>111621</v>
+        <v>111622</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136097946</v>
       </c>
       <c r="B56" t="n">
-        <v>111621</v>
+        <v>111622</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>136097904</v>
       </c>
       <c r="B58" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>136097886</v>
       </c>
       <c r="B59" t="n">
-        <v>102453</v>
+        <v>102454</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136097892</v>
       </c>
       <c r="B60" t="n">
-        <v>102453</v>
+        <v>102454</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136097894</v>
       </c>
       <c r="B61" t="n">
-        <v>102453</v>
+        <v>102454</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136097901</v>
       </c>
       <c r="B62" t="n">
-        <v>102453</v>
+        <v>102454</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>136097903</v>
       </c>
       <c r="B63" t="n">
-        <v>102453</v>
+        <v>102454</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>136097913</v>
       </c>
       <c r="B64" t="n">
-        <v>102453</v>
+        <v>102454</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>136097916</v>
       </c>
       <c r="B65" t="n">
-        <v>102453</v>
+        <v>102454</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>136098084</v>
       </c>
       <c r="B66" t="n">
-        <v>102453</v>
+        <v>102454</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>136097902</v>
       </c>
       <c r="B67" t="n">
-        <v>104337</v>
+        <v>104338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>136097895</v>
       </c>
       <c r="B72" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136097917</v>
       </c>
       <c r="B73" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>136097919</v>
       </c>
       <c r="B74" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136097920</v>
       </c>
       <c r="B75" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>136097940</v>
       </c>
       <c r="B76" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136097945</v>
       </c>
       <c r="B77" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>136097888</v>
       </c>
       <c r="B78" t="n">
-        <v>101439</v>
+        <v>101440</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136097935</v>
       </c>
       <c r="B79" t="n">
-        <v>101439</v>
+        <v>101440</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>136097937</v>
       </c>
       <c r="B80" t="n">
-        <v>101439</v>
+        <v>101440</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2103,7 +2103,7 @@
         <v>136097908</v>
       </c>
       <c r="B15" t="n">
-        <v>96642</v>
+        <v>96655</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136097912</v>
       </c>
       <c r="B16" t="n">
-        <v>96642</v>
+        <v>96655</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136097911</v>
       </c>
       <c r="B22" t="n">
-        <v>96391</v>
+        <v>96404</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136097914</v>
       </c>
       <c r="B27" t="n">
-        <v>96436</v>
+        <v>96449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96663</v>
+        <v>96676</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96663</v>
+        <v>96676</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96663</v>
+        <v>96676</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136101564</v>
       </c>
       <c r="B36" t="n">
-        <v>92145</v>
+        <v>92158</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>136097889</v>
       </c>
       <c r="B47" t="n">
-        <v>111622</v>
+        <v>111635</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>136097891</v>
       </c>
       <c r="B48" t="n">
-        <v>111622</v>
+        <v>111635</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136097893</v>
       </c>
       <c r="B49" t="n">
-        <v>111622</v>
+        <v>111635</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136097900</v>
       </c>
       <c r="B50" t="n">
-        <v>111622</v>
+        <v>111635</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136097921</v>
       </c>
       <c r="B51" t="n">
-        <v>111622</v>
+        <v>111635</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136097933</v>
       </c>
       <c r="B52" t="n">
-        <v>111622</v>
+        <v>111635</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>136097936</v>
       </c>
       <c r="B53" t="n">
-        <v>111622</v>
+        <v>111635</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>136097939</v>
       </c>
       <c r="B54" t="n">
-        <v>111622</v>
+        <v>111635</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136097943</v>
       </c>
       <c r="B55" t="n">
-        <v>111622</v>
+        <v>111635</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136097946</v>
       </c>
       <c r="B56" t="n">
-        <v>111622</v>
+        <v>111635</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>136097904</v>
       </c>
       <c r="B58" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>136097886</v>
       </c>
       <c r="B59" t="n">
-        <v>102454</v>
+        <v>102467</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136097892</v>
       </c>
       <c r="B60" t="n">
-        <v>102454</v>
+        <v>102467</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136097894</v>
       </c>
       <c r="B61" t="n">
-        <v>102454</v>
+        <v>102467</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136097901</v>
       </c>
       <c r="B62" t="n">
-        <v>102454</v>
+        <v>102467</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>136097903</v>
       </c>
       <c r="B63" t="n">
-        <v>102454</v>
+        <v>102467</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>136097913</v>
       </c>
       <c r="B64" t="n">
-        <v>102454</v>
+        <v>102467</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>136097916</v>
       </c>
       <c r="B65" t="n">
-        <v>102454</v>
+        <v>102467</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>136098084</v>
       </c>
       <c r="B66" t="n">
-        <v>102454</v>
+        <v>102467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>136097902</v>
       </c>
       <c r="B67" t="n">
-        <v>104338</v>
+        <v>104351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>136097895</v>
       </c>
       <c r="B72" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136097917</v>
       </c>
       <c r="B73" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>136097919</v>
       </c>
       <c r="B74" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136097920</v>
       </c>
       <c r="B75" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>136097940</v>
       </c>
       <c r="B76" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136097945</v>
       </c>
       <c r="B77" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>136097888</v>
       </c>
       <c r="B78" t="n">
-        <v>101440</v>
+        <v>101453</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136097935</v>
       </c>
       <c r="B79" t="n">
-        <v>101440</v>
+        <v>101453</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>136097937</v>
       </c>
       <c r="B80" t="n">
-        <v>101440</v>
+        <v>101453</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2103,7 +2103,7 @@
         <v>136097908</v>
       </c>
       <c r="B15" t="n">
-        <v>96655</v>
+        <v>96656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136097912</v>
       </c>
       <c r="B16" t="n">
-        <v>96655</v>
+        <v>96656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136097911</v>
       </c>
       <c r="B22" t="n">
-        <v>96404</v>
+        <v>96405</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136097914</v>
       </c>
       <c r="B27" t="n">
-        <v>96449</v>
+        <v>96450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96676</v>
+        <v>96677</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96676</v>
+        <v>96677</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96676</v>
+        <v>96677</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136101564</v>
       </c>
       <c r="B36" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>136097889</v>
       </c>
       <c r="B47" t="n">
-        <v>111635</v>
+        <v>111636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>136097891</v>
       </c>
       <c r="B48" t="n">
-        <v>111635</v>
+        <v>111636</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136097893</v>
       </c>
       <c r="B49" t="n">
-        <v>111635</v>
+        <v>111636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136097900</v>
       </c>
       <c r="B50" t="n">
-        <v>111635</v>
+        <v>111636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136097921</v>
       </c>
       <c r="B51" t="n">
-        <v>111635</v>
+        <v>111636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136097933</v>
       </c>
       <c r="B52" t="n">
-        <v>111635</v>
+        <v>111636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>136097936</v>
       </c>
       <c r="B53" t="n">
-        <v>111635</v>
+        <v>111636</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>136097939</v>
       </c>
       <c r="B54" t="n">
-        <v>111635</v>
+        <v>111636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136097943</v>
       </c>
       <c r="B55" t="n">
-        <v>111635</v>
+        <v>111636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136097946</v>
       </c>
       <c r="B56" t="n">
-        <v>111635</v>
+        <v>111636</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>136097904</v>
       </c>
       <c r="B58" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>136097886</v>
       </c>
       <c r="B59" t="n">
-        <v>102467</v>
+        <v>102468</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136097892</v>
       </c>
       <c r="B60" t="n">
-        <v>102467</v>
+        <v>102468</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136097894</v>
       </c>
       <c r="B61" t="n">
-        <v>102467</v>
+        <v>102468</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136097901</v>
       </c>
       <c r="B62" t="n">
-        <v>102467</v>
+        <v>102468</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>136097903</v>
       </c>
       <c r="B63" t="n">
-        <v>102467</v>
+        <v>102468</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>136097913</v>
       </c>
       <c r="B64" t="n">
-        <v>102467</v>
+        <v>102468</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>136097916</v>
       </c>
       <c r="B65" t="n">
-        <v>102467</v>
+        <v>102468</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>136098084</v>
       </c>
       <c r="B66" t="n">
-        <v>102467</v>
+        <v>102468</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>136097902</v>
       </c>
       <c r="B67" t="n">
-        <v>104351</v>
+        <v>104352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>136097895</v>
       </c>
       <c r="B72" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136097917</v>
       </c>
       <c r="B73" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>136097919</v>
       </c>
       <c r="B74" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136097920</v>
       </c>
       <c r="B75" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>136097940</v>
       </c>
       <c r="B76" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136097945</v>
       </c>
       <c r="B77" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>136097888</v>
       </c>
       <c r="B78" t="n">
-        <v>101453</v>
+        <v>101454</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136097935</v>
       </c>
       <c r="B79" t="n">
-        <v>101453</v>
+        <v>101454</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>136097937</v>
       </c>
       <c r="B80" t="n">
-        <v>101453</v>
+        <v>101454</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
